--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G15">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G21">

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G11">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N34">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N41">

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22">
@@ -3904,55 +3904,55 @@
         <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>2.01</v>
+        <v>3.08</v>
       </c>
       <c r="Q17">
-        <v>3.71</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="U17">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.9</v>
+        <v>4.79</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB17">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AC17">
-        <v>2.93</v>
+        <v>2.21</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF17">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>3.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>3.71</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S18">
+        <v>1.34</v>
+      </c>
+      <c r="T18">
+        <v>3.26</v>
+      </c>
+      <c r="U18">
+        <v>2.63</v>
+      </c>
+      <c r="V18">
+        <v>1.44</v>
+      </c>
+      <c r="W18">
+        <v>1.1</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
         <v>1.22</v>
       </c>
-      <c r="T18">
-        <v>3.75</v>
-      </c>
-      <c r="U18">
-        <v>2.2</v>
-      </c>
-      <c r="V18">
-        <v>1.62</v>
-      </c>
-      <c r="W18">
-        <v>1.15</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.18</v>
-      </c>
       <c r="Z18">
-        <v>4.79</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.93</v>
       </c>
       <c r="AD18">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AG18">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,16 +4586,16 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5081,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G36">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G39">

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G38">

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.99</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>4.01</v>
+        <v>5.55</v>
       </c>
       <c r="P14">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>3.99</v>
       </c>
       <c r="O15">
-        <v>5.55</v>
+        <v>4.01</v>
       </c>
       <c r="P15">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AD15">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3925,7 +3925,7 @@
         <v>1.09</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.16</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="O23">
-        <v>3.89</v>
+        <v>4.16</v>
       </c>
       <c r="P23">
-        <v>3.65</v>
+        <v>4.52</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>4.52</v>
+        <v>3.97</v>
       </c>
       <c r="P24">
-        <v>5.39</v>
+        <v>3.04</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="AA24">
+        <v>1.36</v>
+      </c>
+      <c r="AB24">
+        <v>3.2</v>
+      </c>
+      <c r="AC24">
+        <v>2.25</v>
+      </c>
+      <c r="AD24">
         <v>1.57</v>
       </c>
-      <c r="AB24">
-        <v>2.25</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>11.2</v>
       </c>
       <c r="O25">
-        <v>3.97</v>
+        <v>6.43</v>
       </c>
       <c r="P25">
-        <v>3.04</v>
+        <v>1.3</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD25">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>11.2</v>
+        <v>4.67</v>
       </c>
       <c r="O26">
-        <v>6.43</v>
+        <v>4.31</v>
       </c>
       <c r="P26">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA26">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC26">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>2.07</v>
+      </c>
+      <c r="O27">
+        <v>3.89</v>
+      </c>
+      <c r="P27">
+        <v>3.65</v>
+      </c>
+      <c r="Q27">
         <v>2.71</v>
       </c>
-      <c r="O27">
-        <v>3.75</v>
-      </c>
-      <c r="P27">
-        <v>2.63</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA27">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="O28">
-        <v>4.16</v>
+        <v>4.52</v>
       </c>
       <c r="P28">
-        <v>4.52</v>
+        <v>5.39</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.67</v>
+        <v>2.71</v>
       </c>
       <c r="O29">
-        <v>4.31</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AD29">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5534,34 +5534,34 @@
         <v>3.51</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA32">
         <v>1.88</v>
@@ -5570,19 +5570,19 @@
         <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>10.9</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>3.08</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>3.87</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>11.2</v>
+        <v>4.67</v>
       </c>
       <c r="O25">
-        <v>6.43</v>
+        <v>4.31</v>
       </c>
       <c r="P25">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>8</v>
+        <v>4.02</v>
       </c>
       <c r="R25">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="U25">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="V25">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AA25">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC25">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AF25">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.67</v>
+        <v>11.2</v>
       </c>
       <c r="O26">
-        <v>4.31</v>
+        <v>6.43</v>
       </c>
       <c r="P26">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="Q26">
-        <v>4.02</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="S26">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="V26">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="W26">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB26">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AD26">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE26">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.07</v>
+        <v>2.71</v>
       </c>
       <c r="O27">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>3.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q27">
-        <v>2.71</v>
+        <v>3.57</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T27">
         <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>3.92</v>
+        <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="O28">
-        <v>4.52</v>
+        <v>3.89</v>
       </c>
       <c r="P28">
-        <v>5.39</v>
+        <v>3.65</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
+        <v>2</v>
+      </c>
+      <c r="AC28">
+        <v>2.98</v>
+      </c>
+      <c r="AD28">
+        <v>1.4</v>
+      </c>
+      <c r="AE28">
+        <v>1.13</v>
+      </c>
+      <c r="AF28">
+        <v>1.62</v>
+      </c>
+      <c r="AG28">
         <v>2.25</v>
       </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.71</v>
+        <v>1.64</v>
       </c>
       <c r="O29">
-        <v>3.75</v>
+        <v>4.52</v>
       </c>
       <c r="P29">
-        <v>2.63</v>
+        <v>5.39</v>
       </c>
       <c r="Q29">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC29">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>3.99</v>
       </c>
       <c r="O14">
-        <v>5.55</v>
+        <v>4.01</v>
       </c>
       <c r="P14">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="Q14">
-        <v>5.42</v>
+        <v>4.08</v>
       </c>
       <c r="R14">
-        <v>3.02</v>
+        <v>2.36</v>
       </c>
       <c r="S14">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="U14">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>6.4</v>
+        <v>5.09</v>
       </c>
       <c r="AA14">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AD14">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE14">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.99</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>4.01</v>
+        <v>5.55</v>
       </c>
       <c r="P15">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="Q15">
-        <v>4.08</v>
+        <v>5.42</v>
       </c>
       <c r="R15">
-        <v>2.36</v>
+        <v>3.02</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T15">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>5.09</v>
+        <v>6.4</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="AC15">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AD15">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AE15">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AF15">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK15">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.67</v>
+        <v>11.2</v>
       </c>
       <c r="O25">
-        <v>4.31</v>
+        <v>6.43</v>
       </c>
       <c r="P25">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="Q25">
-        <v>4.02</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="V25">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="W25">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB25">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE25">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>11.2</v>
+        <v>2.71</v>
       </c>
       <c r="O26">
-        <v>6.43</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>3.57</v>
       </c>
       <c r="R26">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V26">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA26">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AD26">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AE26">
+        <v>1.25</v>
+      </c>
+      <c r="AF26">
+        <v>1.5</v>
+      </c>
+      <c r="AG26">
+        <v>2.5</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.23</v>
       </c>
-      <c r="AF26">
-        <v>1.85</v>
-      </c>
-      <c r="AG26">
-        <v>1.87</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.12</v>
-      </c>
       <c r="AK26">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.71</v>
+        <v>4.67</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>4.31</v>
       </c>
       <c r="P27">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="Q27">
-        <v>3.57</v>
+        <v>4.02</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S27">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="U27">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="V27">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="W27">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
+        <v>1.04</v>
+      </c>
+      <c r="Z27">
+        <v>6.75</v>
+      </c>
+      <c r="AA27">
+        <v>1.35</v>
+      </c>
+      <c r="AB27">
+        <v>3.2</v>
+      </c>
+      <c r="AC27">
+        <v>2.3</v>
+      </c>
+      <c r="AD27">
+        <v>1.55</v>
+      </c>
+      <c r="AE27">
+        <v>1.38</v>
+      </c>
+      <c r="AF27">
+        <v>1.4</v>
+      </c>
+      <c r="AG27">
+        <v>2.62</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.21</v>
+      </c>
+      <c r="AK27">
         <v>1.15</v>
-      </c>
-      <c r="Z27">
-        <v>5.25</v>
-      </c>
-      <c r="AA27">
-        <v>1.68</v>
-      </c>
-      <c r="AB27">
-        <v>2.05</v>
-      </c>
-      <c r="AC27">
-        <v>2.42</v>
-      </c>
-      <c r="AD27">
-        <v>1.66</v>
-      </c>
-      <c r="AE27">
-        <v>1.25</v>
-      </c>
-      <c r="AF27">
-        <v>1.5</v>
-      </c>
-      <c r="AG27">
-        <v>2.5</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.23</v>
-      </c>
-      <c r="AK27">
-        <v>1.34</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>11.2</v>
       </c>
       <c r="O24">
-        <v>3.97</v>
+        <v>6.43</v>
       </c>
       <c r="P24">
-        <v>3.04</v>
+        <v>1.3</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="S24">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="V24">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="W24">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>6.18</v>
+        <v>5</v>
       </c>
       <c r="AA24">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB24">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AE24">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK24">
-        <v>1.71</v>
+        <v>1.05</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>11.2</v>
+        <v>2.71</v>
       </c>
       <c r="O25">
-        <v>6.43</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q25">
-        <v>8</v>
+        <v>3.57</v>
       </c>
       <c r="R25">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V25">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA25">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AD25">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AE25">
+        <v>1.25</v>
+      </c>
+      <c r="AF25">
+        <v>1.5</v>
+      </c>
+      <c r="AG25">
+        <v>2.5</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.23</v>
       </c>
-      <c r="AF25">
-        <v>1.85</v>
-      </c>
-      <c r="AG25">
-        <v>1.87</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.12</v>
-      </c>
       <c r="AK25">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.71</v>
+        <v>4.67</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>4.31</v>
       </c>
       <c r="P26">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
-        <v>3.57</v>
+        <v>4.02</v>
       </c>
       <c r="R26">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S26">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="U26">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="V26">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
+        <v>1.04</v>
+      </c>
+      <c r="Z26">
+        <v>6.75</v>
+      </c>
+      <c r="AA26">
+        <v>1.35</v>
+      </c>
+      <c r="AB26">
+        <v>3.2</v>
+      </c>
+      <c r="AC26">
+        <v>2.3</v>
+      </c>
+      <c r="AD26">
+        <v>1.55</v>
+      </c>
+      <c r="AE26">
+        <v>1.38</v>
+      </c>
+      <c r="AF26">
+        <v>1.4</v>
+      </c>
+      <c r="AG26">
+        <v>2.62</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.21</v>
+      </c>
+      <c r="AK26">
         <v>1.15</v>
-      </c>
-      <c r="Z26">
-        <v>5.25</v>
-      </c>
-      <c r="AA26">
-        <v>1.68</v>
-      </c>
-      <c r="AB26">
-        <v>2.05</v>
-      </c>
-      <c r="AC26">
-        <v>2.42</v>
-      </c>
-      <c r="AD26">
-        <v>1.66</v>
-      </c>
-      <c r="AE26">
-        <v>1.25</v>
-      </c>
-      <c r="AF26">
-        <v>1.5</v>
-      </c>
-      <c r="AG26">
-        <v>2.5</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.23</v>
-      </c>
-      <c r="AK26">
-        <v>1.34</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.67</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="P27">
-        <v>1.76</v>
+        <v>3.04</v>
       </c>
       <c r="Q27">
-        <v>4.02</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="S27">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="T27">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="U27">
         <v>2.04</v>
@@ -4737,37 +4737,37 @@
         <v>1.82</v>
       </c>
       <c r="W27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>6.75</v>
+        <v>6.18</v>
       </c>
       <c r="AA27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB27">
         <v>3.2</v>
       </c>
       <c r="AC27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD27">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.15</v>
+        <v>1.71</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -985,13 +985,13 @@
         <v>3.3</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.37</v>
@@ -1000,25 +1000,25 @@
         <v>2.66</v>
       </c>
       <c r="AA4">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AB4">
         <v>1.55</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
         <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
         <v>1.92</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
         <v>1.57</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.67</v>
+        <v>2.3</v>
       </c>
       <c r="O26">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="P26">
-        <v>1.76</v>
+        <v>3.04</v>
       </c>
       <c r="Q26">
-        <v>4.02</v>
+        <v>2.55</v>
       </c>
       <c r="R26">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="S26">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="T26">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="U26">
         <v>2.04</v>
@@ -4574,37 +4574,37 @@
         <v>1.82</v>
       </c>
       <c r="W26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>6.75</v>
+        <v>6.18</v>
       </c>
       <c r="AA26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB26">
         <v>3.2</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD26">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE26">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.15</v>
+        <v>1.71</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>4.67</v>
       </c>
       <c r="O27">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="P27">
-        <v>3.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q27">
-        <v>2.55</v>
+        <v>4.02</v>
       </c>
       <c r="R27">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S27">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="T27">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="U27">
         <v>2.04</v>
@@ -4737,37 +4737,37 @@
         <v>1.82</v>
       </c>
       <c r="W27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z27">
-        <v>6.18</v>
+        <v>6.75</v>
       </c>
       <c r="AA27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB27">
         <v>3.2</v>
       </c>
       <c r="AC27">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AF27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.71</v>
+        <v>1.15</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-11-04.xlsx
+++ b/jogos_2026-11-04.xlsx
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S19">
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.44</v>
@@ -3436,34 +3436,34 @@
         <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AA19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC19">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD19">
         <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AL19">
         <v>0</v>
